--- a/exports/Autoslash_supplier_list_2026-05-21.xlsx
+++ b/exports/Autoslash_supplier_list_2026-05-21.xlsx
@@ -528,7 +528,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Export date: 2026-05-21   |   Question: Export to Excel: which suppliers does Autoslash have?</t>
+          <t>Export date: 2026-05-21   |   Question: which suppliers does Autoslash have?. provide excel</t>
         </is>
       </c>
     </row>
